--- a/dataset_t6_grouped/results2/G4/G4_T2S0007_W0047F0001T0006Z000C1N51_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T2S0007_W0047F0001T0006Z000C1N51_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>6.687829607009242</v>
+        <v>1.086772311139002</v>
       </c>
       <c r="D2" t="n">
-        <v>6.45979421731462</v>
+        <v>1.049716560313626</v>
       </c>
       <c r="E2" t="n">
-        <v>15.84132079786429</v>
+        <v>2.574214629652947</v>
       </c>
       <c r="F2" t="n">
-        <v>10.99050104473502</v>
+        <v>1.785956419769441</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>52.33947453289675</v>
+        <v>8.505164611595722</v>
       </c>
       <c r="D3" t="n">
-        <v>40.14979667245535</v>
+        <v>6.524341959273994</v>
       </c>
       <c r="E3" t="n">
-        <v>15.84132079786429</v>
+        <v>2.574214629652947</v>
       </c>
       <c r="F3" t="n">
-        <v>10.99050104473502</v>
+        <v>1.785956419769441</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>12.16283603573818</v>
+        <v>1.976460855807454</v>
       </c>
       <c r="D4" t="n">
-        <v>16.56768288996771</v>
+        <v>2.692248469619752</v>
       </c>
       <c r="E4" t="n">
-        <v>15.84132079786429</v>
+        <v>2.574214629652947</v>
       </c>
       <c r="F4" t="n">
-        <v>10.99050104473502</v>
+        <v>1.785956419769441</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>19.76301089961147</v>
+        <v>3.211489271186863</v>
       </c>
       <c r="D5" t="n">
-        <v>19.9816961490087</v>
+        <v>3.247025624213914</v>
       </c>
       <c r="E5" t="n">
-        <v>15.84132079786429</v>
+        <v>2.574214629652947</v>
       </c>
       <c r="F5" t="n">
-        <v>10.99050104473502</v>
+        <v>1.785956419769441</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>23.23490916794191</v>
+        <v>3.775672739790561</v>
       </c>
       <c r="D6" t="n">
-        <v>23.36795030709812</v>
+        <v>3.797291924903445</v>
       </c>
       <c r="E6" t="n">
-        <v>15.84132079786429</v>
+        <v>2.574214629652947</v>
       </c>
       <c r="F6" t="n">
-        <v>10.99050104473502</v>
+        <v>1.785956419769441</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
